--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2600,6 +2600,136 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130692268</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56779</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>600760</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6503681</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjolårsunge.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2605,7 +2605,7 @@
         <v>130692268</v>
       </c>
       <c r="B16" t="n">
-        <v>56779</v>
+        <v>56781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2729,6 +2729,281 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130705002</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56797</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>600814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6503707</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130704777</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56790</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100041</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Coronella austriaca</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dräktig hona</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>600814</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6503707</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två dräktiga honor på samma plats.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -2605,7 +2605,7 @@
         <v>130692268</v>
       </c>
       <c r="B16" t="n">
-        <v>56781</v>
+        <v>56789</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>130705002</v>
       </c>
       <c r="B17" t="n">
-        <v>56797</v>
+        <v>56805</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>130704777</v>
       </c>
       <c r="B18" t="n">
-        <v>56790</v>
+        <v>56798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -2605,7 +2605,7 @@
         <v>130692268</v>
       </c>
       <c r="B16" t="n">
-        <v>56789</v>
+        <v>56790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>130705002</v>
       </c>
       <c r="B17" t="n">
-        <v>56805</v>
+        <v>56806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>130704777</v>
       </c>
       <c r="B18" t="n">
-        <v>56798</v>
+        <v>56799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3005,6 +3005,276 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130962087</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>600790</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6503701</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130966161</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56799</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100041</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Coronella austriaca</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>dräktig hona</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>600812</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6503712</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -3143,7 +3143,7 @@
         <v>130966161</v>
       </c>
       <c r="B20" t="n">
-        <v>56819</v>
+        <v>56821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -3143,7 +3143,7 @@
         <v>130966161</v>
       </c>
       <c r="B20" t="n">
-        <v>56821</v>
+        <v>56822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -3143,7 +3143,7 @@
         <v>130966161</v>
       </c>
       <c r="B20" t="n">
-        <v>56822</v>
+        <v>56823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -3143,7 +3143,7 @@
         <v>130966161</v>
       </c>
       <c r="B20" t="n">
-        <v>56823</v>
+        <v>56826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -3143,7 +3143,7 @@
         <v>130966161</v>
       </c>
       <c r="B20" t="n">
-        <v>56826</v>
+        <v>56827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92423460</v>
+        <v>92431362</v>
       </c>
       <c r="B2" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>100041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -723,11 +718,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
@@ -740,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600794.9881290058</v>
+        <v>600808</v>
       </c>
       <c r="R2" t="n">
-        <v>6503700.198015673</v>
+        <v>6503710</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,22 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2020-05-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2020-05-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,15 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92431362</v>
+        <v>98712463</v>
       </c>
       <c r="B3" t="n">
-        <v>57133</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,7 +847,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -874,13 +864,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600807.7716597053</v>
+        <v>600815</v>
       </c>
       <c r="R3" t="n">
-        <v>6503709.897264228</v>
+        <v>6503712</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,22 +894,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-30</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-30</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tre höggravida honor som solade på samma plats inom några meter från varandra.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,15 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98712661</v>
+        <v>105037079</v>
       </c>
       <c r="B4" t="n">
-        <v>55599</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,21 +953,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100070</v>
+        <v>100041</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -990,13 +980,13 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ömsskinn</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1004,14 +994,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nävsjön, Srm</t>
+          <t>Nävsjön, Tindered, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600825.9407833308</v>
+        <v>600828</v>
       </c>
       <c r="R4" t="n">
-        <v>6503712.970341578</v>
+        <v>6503704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,22 +1028,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,15 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98712463</v>
+        <v>113970806</v>
       </c>
       <c r="B5" t="n">
-        <v>57133</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1101,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1134,7 +1119,11 @@
           <t>hona</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>dräktig hona</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1142,17 +1131,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nävsjön, Srm</t>
+          <t>Nävsjön, Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600815.0258341612</v>
+        <v>600819</v>
       </c>
       <c r="R5" t="n">
-        <v>6503711.646580339</v>
+        <v>6503711</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,27 +1165,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tre höggravida honor som solade på samma plats inom några meter från varandra.</t>
+          <t>Fen dräktiga honor i direkt närhet av varandra, solande.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1217,44 +1206,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Stefan Andersson, Håkan Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105039298</v>
+        <v>114375154</v>
       </c>
       <c r="B6" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208257</v>
+        <v>100041</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1267,11 +1251,19 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>dräktig hona</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1281,14 +1273,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nävsjön, Nävsjön, Srm</t>
+          <t>Nävsjön, Svanviken, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600746.4947945587</v>
+        <v>600825</v>
       </c>
       <c r="R6" t="n">
-        <v>6503680.205800339</v>
+        <v>6503718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,27 +1307,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Subadult.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,22 +1343,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Stefan Andersson, Håkan Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105039272</v>
+        <v>118374125</v>
       </c>
       <c r="B7" t="n">
-        <v>55599</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,59 +1361,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100070</v>
+        <v>100041</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nävsjön, Nävsjön, Srm</t>
+          <t>Nävsjön, campingen , Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600820.2093091698</v>
+        <v>600778</v>
       </c>
       <c r="R7" t="n">
-        <v>6503712.821800501</v>
+        <v>6503690</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1458,22 +1424,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1489,27 +1455,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Hans Norelius</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Hans Norelius, Eva Edmert</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105036574</v>
+        <v>130704777</v>
       </c>
       <c r="B8" t="n">
-        <v>55599</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1517,26 +1478,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100070</v>
+        <v>100041</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1546,13 +1507,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>dräktig hona</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1566,10 +1531,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600810.0175624175</v>
+        <v>600814</v>
       </c>
       <c r="R8" t="n">
-        <v>6503703.710122162</v>
+        <v>6503707</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1596,22 +1561,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Två dräktiga honor på samma plats.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1639,15 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113970879</v>
+        <v>130966161</v>
       </c>
       <c r="B9" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,26 +1620,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100070</v>
+        <v>100041</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1684,13 +1649,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>dräktig hona</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1700,14 +1669,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nävsjön, Nävsjön, Srm</t>
+          <t>Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600819</v>
+        <v>600812</v>
       </c>
       <c r="R9" t="n">
-        <v>6503711</v>
+        <v>6503712</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1734,22 +1703,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1770,39 +1739,34 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Håkan Jansson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113970886</v>
+        <v>76800985</v>
       </c>
       <c r="B10" t="n">
-        <v>56223</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208257</v>
+        <v>100070</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1812,7 +1776,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1825,10 +1789,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1838,17 +1806,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nävsjön, Nävsjön, Srm</t>
+          <t>Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600819</v>
+        <v>600762</v>
       </c>
       <c r="R10" t="n">
-        <v>6503711</v>
+        <v>6503673</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1872,22 +1840,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1908,49 +1876,44 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Håkan Jansson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113971888</v>
+        <v>98712477</v>
       </c>
       <c r="B11" t="n">
-        <v>56252</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208260</v>
+        <v>100070</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1960,19 +1923,11 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>dräktig hona</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1980,17 +1935,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nävsjön, Nävsjön, Srm</t>
+          <t>Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600819</v>
+        <v>600762</v>
       </c>
       <c r="R11" t="n">
-        <v>6503711</v>
+        <v>6503672</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2014,22 +1969,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2050,22 +2005,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Håkan Jansson, Rickard Malmström</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113971599</v>
+        <v>98712661</v>
       </c>
       <c r="B12" t="n">
-        <v>56235</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,26 +2023,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100041</v>
+        <v>100070</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2102,19 +2052,11 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>dräktig hona</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2122,17 +2064,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nävsjön, Nävsjön, Srm</t>
+          <t>Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600819</v>
+        <v>600826</v>
       </c>
       <c r="R12" t="n">
-        <v>6503711</v>
+        <v>6503713</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,22 +2098,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2192,22 +2134,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Håkan Jansson, Rickard Malmström</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114375188</v>
+        <v>105036574</v>
       </c>
       <c r="B13" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,7 +2171,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2248,7 +2185,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2256,14 +2197,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nävsjön, Svanviken, Srm</t>
+          <t>Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600863</v>
+        <v>600810</v>
       </c>
       <c r="R13" t="n">
-        <v>6503721</v>
+        <v>6503704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2290,27 +2231,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bild på endast ena individen.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2331,22 +2267,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Håkan Jansson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114375154</v>
+        <v>105039272</v>
       </c>
       <c r="B14" t="n">
-        <v>56235</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2354,21 +2285,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100041</v>
+        <v>100070</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2383,17 +2314,13 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>dräktig hona</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2403,17 +2330,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nävsjön, Svanviken, Srm</t>
+          <t>Nävsjön, Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600825</v>
+        <v>600820</v>
       </c>
       <c r="R14" t="n">
-        <v>6503718</v>
+        <v>6503713</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2437,22 +2364,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2022-08-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2473,22 +2400,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Håkan Jansson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118374125</v>
+        <v>113970879</v>
       </c>
       <c r="B15" t="n">
-        <v>56334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2496,43 +2418,59 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100041</v>
+        <v>100070</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nävsjön, campingen , Srm</t>
+          <t>Nävsjön, Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600778</v>
+        <v>600819</v>
       </c>
       <c r="R15" t="n">
-        <v>6503690</v>
+        <v>6503711</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2559,22 +2497,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2590,22 +2528,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hans Norelius</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hans Norelius, Eva Edmert</t>
+          <t>Stefan Andersson, Håkan Jansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130692268</v>
+        <v>113971974</v>
       </c>
       <c r="B16" t="n">
-        <v>56810</v>
+        <v>56879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2640,8 +2578,16 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -2650,14 +2596,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nävsjön, Srm</t>
+          <t>Nävsjön, Nävsjön, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600760</v>
+        <v>600757</v>
       </c>
       <c r="R16" t="n">
-        <v>6503681</v>
+        <v>6503674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2684,27 +2630,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjolårsunge.</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2725,39 +2666,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Stefan Andersson, Håkan Jansson, Rickard Malmström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130705002</v>
+        <v>114375127</v>
       </c>
       <c r="B17" t="n">
-        <v>56826</v>
+        <v>56879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100088</v>
+        <v>100070</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2788,14 +2729,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nävsjön, Srm</t>
+          <t>Nävsjön, Svanviken, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600814</v>
+        <v>600731</v>
       </c>
       <c r="R17" t="n">
-        <v>6503707</v>
+        <v>6503682</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2822,22 +2763,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2858,17 +2799,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Stefan Andersson, Håkan Jansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130704777</v>
+        <v>114375188</v>
       </c>
       <c r="B18" t="n">
-        <v>56819</v>
+        <v>56879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2876,21 +2817,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100041</v>
+        <v>100070</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2905,19 +2846,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>dräktig hona</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2925,14 +2858,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nävsjön, Srm</t>
+          <t>Nävsjön, Svanviken, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600814</v>
+        <v>600863</v>
       </c>
       <c r="R18" t="n">
-        <v>6503707</v>
+        <v>6503721</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2959,27 +2892,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Två dräktiga honor på samma plats.</t>
+          <t>Bild på endast ena individen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3000,39 +2933,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Stefan Andersson, Håkan Jansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130962087</v>
+        <v>130692268</v>
       </c>
       <c r="B19" t="n">
-        <v>56836</v>
+        <v>56879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208260</v>
+        <v>100070</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3045,16 +2978,8 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
@@ -3067,10 +2992,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600790</v>
+        <v>600760</v>
       </c>
       <c r="R19" t="n">
-        <v>6503701</v>
+        <v>6503681</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3097,22 +3022,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fjolårsunge.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3140,37 +3070,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130966161</v>
+        <v>130705002</v>
       </c>
       <c r="B20" t="n">
-        <v>56833</v>
+        <v>56895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100041</v>
+        <v>100088</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3188,11 +3118,7 @@
           <t>hona</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>dräktig hona</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3204,13 +3130,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600812</v>
+        <v>600814</v>
       </c>
       <c r="R20" t="n">
-        <v>6503712</v>
+        <v>6503707</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3234,22 +3160,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3274,6 +3200,676 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>92423460</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>600795</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6503700</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105039298</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nävsjön, Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>600746</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6503680</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Subadult.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113970886</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nävsjön, Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>600819</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6503711</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Håkan Jansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113971888</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>dräktig hona</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nävsjön, Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>600819</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6503711</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Håkan Jansson, Rickard Malmström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130962087</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nävsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>600790</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6503701</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56727-2025 artfynd.xlsx
+++ b/artfynd/A 56727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92431362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -939,6 +949,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98712463</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1068,6 +1083,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105037079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1210,6 +1230,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113970806</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1347,6 +1372,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114375154</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1464,6 +1494,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118374125</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1606,6 +1641,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130704777</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1743,6 +1783,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130966161</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1880,6 +1925,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76800985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2009,6 +2059,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98712477</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2138,6 +2193,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98712661</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2271,6 +2331,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105036574</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2404,6 +2469,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105039272</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2537,6 +2607,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113970879</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2670,6 +2745,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113971974</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2803,6 +2883,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114375127</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2937,6 +3022,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114375188</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3067,6 +3157,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130692268</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3200,6 +3295,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130705002</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3333,6 +3433,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92423460</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3467,6 +3572,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105039298</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3600,6 +3710,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113970886</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3737,6 +3852,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113971888</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3870,8 +3990,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>